--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487952_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487952_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C. MORTELLARO</t>
+          <t>J. AGUERA ZEA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.9395</v>
+        <v>2.0907</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.0062</v>
+        <v>1.415</v>
       </c>
       <c r="F2" t="n">
-        <v>2.9457</v>
+        <v>0.6757</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.1456</v>
+        <v>1.0943</v>
       </c>
       <c r="H2" t="n">
-        <v>1.5266</v>
+        <v>0.1127</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.6722</v>
+        <v>0.9816</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.0087</v>
+        <v>1.7274</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1487</v>
+        <v>-0.5782</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.1574</v>
+        <v>2.3057</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8631</v>
+        <v>-0.6331</v>
       </c>
       <c r="N2" t="n">
-        <v>1.3779</v>
+        <v>0.6909</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.5148</v>
+        <v>-1.3241</v>
       </c>
       <c r="P2" t="n">
-        <v>0.7929</v>
+        <v>0.1982</v>
       </c>
       <c r="Q2" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R2" t="n">
-        <v>1.784</v>
+        <v>1.1893</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8908</v>
+        <v>-0.4763</v>
       </c>
       <c r="T2" t="n">
-        <v>0.727</v>
+        <v>-0.5285</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1638</v>
+        <v>0.0521</v>
       </c>
       <c r="V2" t="n">
-        <v>0.4014</v>
+        <v>1.2745</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2666</v>
+        <v>1.2071</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1348</v>
+        <v>0.0674</v>
       </c>
     </row>
     <row r="3">
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6069</v>
+        <v>1.6454</v>
       </c>
       <c r="E3" t="n">
-        <v>0.131</v>
+        <v>0.0292</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4759</v>
+        <v>1.6163</v>
       </c>
       <c r="G3" t="n">
         <v>0.976</v>
@@ -688,13 +688,13 @@
         <v>0.7929</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2294</v>
+        <v>-0.1909</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1176</v>
+        <v>0.0157</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.347</v>
+        <v>-0.2066</v>
       </c>
       <c r="V3" t="n">
         <v>0.0674</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. AGUERA ZEA</t>
+          <t>J. LEGANOVIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4118</v>
+        <v>1.4701</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8203</v>
+        <v>0.7755</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5915</v>
+        <v>0.6946</v>
       </c>
       <c r="G5" t="n">
-        <v>1.0943</v>
+        <v>-0.2243</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1127</v>
+        <v>-0.7466</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9816</v>
+        <v>0.5223</v>
       </c>
       <c r="J5" t="n">
-        <v>1.7274</v>
+        <v>0.0281</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.5782</v>
+        <v>-0.6186</v>
       </c>
       <c r="L5" t="n">
-        <v>2.3057</v>
+        <v>0.6467000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6331</v>
+        <v>-0.2524</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6909</v>
+        <v>-0.128</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.3241</v>
+        <v>-0.1244</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1982</v>
+        <v>0.9911</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1893</v>
+        <v>0.9911</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.1552</v>
+        <v>-0.5038</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.1232</v>
+        <v>-0.4597</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0321</v>
+        <v>-0.0441</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2745</v>
+        <v>1.2071</v>
       </c>
       <c r="W5" t="n">
         <v>1.2071</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0674</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. LEGANOVIC</t>
+          <t>C. MORTELLARO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1935</v>
+        <v>1.1505</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6113</v>
+        <v>-1.4302</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5823</v>
+        <v>2.5806</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2243</v>
+        <v>-0.1456</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7466</v>
+        <v>1.5266</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5223</v>
+        <v>-1.6722</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0281</v>
+        <v>-1.0087</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6186</v>
+        <v>0.1487</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6467000000000001</v>
+        <v>-1.1574</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2524</v>
+        <v>0.8631</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.128</v>
+        <v>1.3779</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1244</v>
+        <v>-0.5148</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9911</v>
+        <v>0.7929</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9911</v>
+        <v>1.784</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7804</v>
+        <v>0.1018</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.624</v>
+        <v>0.303</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1564</v>
+        <v>-0.2012</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2071</v>
+        <v>0.4014</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2071</v>
+        <v>0.2666</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.1348</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K. DIKE EGUN</t>
+          <t>I. DIMITROV KOLEV</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4479</v>
+        <v>-0.1099</v>
       </c>
       <c r="E7" t="n">
-        <v>0.955</v>
+        <v>-1.147</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.4029</v>
+        <v>1.0371</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1024</v>
+        <v>-0.473</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.6004</v>
+        <v>-0.5207000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>1.7028</v>
+        <v>0.0477</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2207</v>
+        <v>-0.4377</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.0689</v>
+        <v>-0.5984</v>
       </c>
       <c r="L7" t="n">
-        <v>1.2896</v>
+        <v>0.1607</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1184</v>
+        <v>-0.0353</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5315</v>
+        <v>0.07770000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4132</v>
+        <v>-0.113</v>
       </c>
       <c r="P7" t="n">
-        <v>1.3876</v>
+        <v>1.784</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3876</v>
+        <v>1.784</v>
       </c>
       <c r="S7" t="n">
-        <v>0.743</v>
+        <v>-1.2922</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7343</v>
+        <v>-0.7093</v>
       </c>
       <c r="U7" t="n">
-        <v>0.008699999999999999</v>
+        <v>-0.5829</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.6808</v>
+        <v>-0.1288</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.6808</v>
+        <v>-0.1288</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. DIMITROV KOLEV</t>
+          <t>K. DIKE EGUN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5955</v>
+        <v>-1.0633</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.4361</v>
+        <v>0.5081</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8405</v>
+        <v>-1.5714</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.473</v>
+        <v>0.1024</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5207000000000001</v>
+        <v>-1.6004</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0477</v>
+        <v>1.7028</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.4377</v>
+        <v>0.2207</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5984</v>
+        <v>-1.0689</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1607</v>
+        <v>1.2896</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0353</v>
+        <v>-0.1184</v>
       </c>
       <c r="N8" t="n">
-        <v>0.07770000000000001</v>
+        <v>-0.5315</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.113</v>
+        <v>0.4132</v>
       </c>
       <c r="P8" t="n">
-        <v>1.784</v>
+        <v>1.3876</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.784</v>
+        <v>1.3876</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.7778</v>
+        <v>0.1276</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9984</v>
+        <v>0.2873</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7794</v>
+        <v>-0.1598</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.1288</v>
+        <v>-2.6808</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1288</v>
+        <v>-2.6808</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. MARKOTA</t>
+          <t>H. VAZQUEZ GARCIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.2917</v>
+        <v>-1.9699</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.8056</v>
+        <v>-4.0614</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5139</v>
+        <v>2.0915</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3604</v>
+        <v>3.4501</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6899999999999999</v>
+        <v>-1.442</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.0503</v>
+        <v>4.8921</v>
       </c>
       <c r="J9" t="n">
-        <v>0.02</v>
+        <v>2.5229</v>
       </c>
       <c r="K9" t="n">
-        <v>1.2176</v>
+        <v>-2.3464</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.1975</v>
+        <v>4.8693</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3804</v>
+        <v>0.9273</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5276</v>
+        <v>0.9045</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1472</v>
+        <v>0.0228</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.784</v>
+        <v>-4.7574</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.9733</v>
+        <v>-6.9378</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1893</v>
+        <v>2.1805</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7228</v>
+        <v>-0.2643</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4847</v>
+        <v>0.3535</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2381</v>
+        <v>-0.6179</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.8701</v>
+        <v>-0.3984</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.337</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5331</v>
+        <v>-0.3984</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>H. VAZQUEZ GARCIA</t>
+          <t>P. MARKOTA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4908</v>
+        <v>-2.3592</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.5542</v>
+        <v>-2.8451</v>
       </c>
       <c r="F10" t="n">
-        <v>2.0634</v>
+        <v>0.4858</v>
       </c>
       <c r="G10" t="n">
-        <v>3.4501</v>
+        <v>-0.3604</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.442</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>4.8921</v>
+        <v>-1.0503</v>
       </c>
       <c r="J10" t="n">
-        <v>2.5229</v>
+        <v>0.02</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.3464</v>
+        <v>1.2176</v>
       </c>
       <c r="L10" t="n">
-        <v>4.8693</v>
+        <v>-1.1975</v>
       </c>
       <c r="M10" t="n">
-        <v>0.9273</v>
+        <v>-0.3804</v>
       </c>
       <c r="N10" t="n">
-        <v>0.9045</v>
+        <v>-0.5276</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0228</v>
+        <v>0.1472</v>
       </c>
       <c r="P10" t="n">
-        <v>-4.7574</v>
+        <v>-1.784</v>
       </c>
       <c r="Q10" t="n">
-        <v>-6.9378</v>
+        <v>-2.9733</v>
       </c>
       <c r="R10" t="n">
-        <v>2.1805</v>
+        <v>1.1893</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7852</v>
+        <v>0.6553</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1393</v>
+        <v>0.4452</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6459</v>
+        <v>0.21</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3984</v>
+        <v>-0.8701</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.337</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.3984</v>
+        <v>-0.5331</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.2807</v>
+        <v>-3.4324</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.2646</v>
+        <v>-4.5286</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9839</v>
+        <v>1.0962</v>
       </c>
       <c r="G11" t="n">
         <v>-1.4761</v>
@@ -1312,13 +1312,13 @@
         <v>1.9822</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1365</v>
+        <v>-0.2882</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8184</v>
+        <v>-0.0824</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3181</v>
+        <v>-0.2058</v>
       </c>
       <c r="V11" t="n">
         <v>-0.677</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.892</v>
+        <v>-6.0209</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.6265</v>
+        <v>-8.643000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>2.7345</v>
+        <v>2.6221</v>
       </c>
       <c r="G12" t="n">
         <v>-6.4871</v>
@@ -1390,13 +1390,13 @@
         <v>2.5769</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1123</v>
+        <v>-0.0165</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2279</v>
+        <v>0.2113</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1156</v>
+        <v>-0.2279</v>
       </c>
       <c r="V12" t="n">
         <v>0.8792</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.338900000000001</v>
+        <v>-7.0909</v>
       </c>
       <c r="E13" t="n">
-        <v>-19.6676</v>
+        <v>-18.4195</v>
       </c>
       <c r="F13" t="n">
-        <v>11.3287</v>
+        <v>11.3285</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.035699999999999</v>
+        <v>-2.0357</v>
       </c>
       <c r="H13" t="n">
         <v>-4.0159</v>
@@ -1441,7 +1441,7 @@
         <v>1.9804</v>
       </c>
       <c r="J13" t="n">
-        <v>-4.429499999999999</v>
+        <v>-4.4295</v>
       </c>
       <c r="K13" t="n">
         <v>-8.2477</v>
@@ -1468,16 +1468,16 @@
         <v>15.8578</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.3956</v>
+        <v>-2.1475</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.4118</v>
+        <v>-0.1639</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.9839</v>
+        <v>-1.9841</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.9255</v>
+        <v>-0.9255000000000004</v>
       </c>
       <c r="W13" t="n">
         <v>4.0136</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.2001</v>
+        <v>4.488</v>
       </c>
       <c r="E14" t="n">
-        <v>0.77</v>
+        <v>0.9737</v>
       </c>
       <c r="F14" t="n">
-        <v>3.4301</v>
+        <v>3.5143</v>
       </c>
       <c r="G14" t="n">
         <v>1.9639</v>
@@ -1546,13 +1546,13 @@
         <v>2.9733</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8322000000000001</v>
+        <v>-0.5443</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4844</v>
+        <v>-0.2806</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3479</v>
+        <v>-0.2636</v>
       </c>
       <c r="V14" t="n">
         <v>2.0772</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.9173</v>
+        <v>2.3525</v>
       </c>
       <c r="E15" t="n">
-        <v>0.801</v>
+        <v>0.08790000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>3.1162</v>
+        <v>2.2645</v>
       </c>
       <c r="G15" t="n">
         <v>2.2118</v>
@@ -1624,13 +1624,13 @@
         <v>2.1805</v>
       </c>
       <c r="S15" t="n">
-        <v>3.5599</v>
+        <v>1.9951</v>
       </c>
       <c r="T15" t="n">
-        <v>1.3327</v>
+        <v>0.6197</v>
       </c>
       <c r="U15" t="n">
-        <v>2.2271</v>
+        <v>1.3754</v>
       </c>
       <c r="V15" t="n">
         <v>-0.0704</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.6503</v>
+        <v>2.1866</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2375</v>
+        <v>-0.17</v>
       </c>
       <c r="F16" t="n">
-        <v>2.4127</v>
+        <v>2.3566</v>
       </c>
       <c r="G16" t="n">
         <v>1.0908</v>
@@ -1702,13 +1702,13 @@
         <v>1.784</v>
       </c>
       <c r="S16" t="n">
-        <v>1.174</v>
+        <v>0.7103</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5911999999999999</v>
+        <v>0.1837</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5827</v>
+        <v>0.5266</v>
       </c>
       <c r="V16" t="n">
         <v>-0.4074</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.3681</v>
+        <v>2.0844</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0833</v>
+        <v>0.3242</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4514</v>
+        <v>1.7603</v>
       </c>
       <c r="G17" t="n">
         <v>-0.0185</v>
@@ -1780,13 +1780,13 @@
         <v>1.784</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9503</v>
+        <v>-0.234</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7781</v>
+        <v>-0.3706</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1723</v>
+        <v>0.1366</v>
       </c>
       <c r="V17" t="n">
         <v>1.5441</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. BOTAS FERNANDEZ</t>
+          <t>L. SIGISMONTI RODRÍGUEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.0016</v>
+        <v>0.6027</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.715</v>
+        <v>0.6027</v>
       </c>
       <c r="F19" t="n">
-        <v>2.7166</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5044999999999999</v>
+        <v>0.6027</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7008</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.2053</v>
+        <v>0.6027</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.3444</v>
+        <v>0.6027</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6653</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6791</v>
+        <v>0.6027</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8399</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1.3661</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5262</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7929</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.784</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7131999999999999</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6205000000000001</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0927</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. SIGISMONTI RODRÍGUEZ</t>
+          <t>M. BOTAS FERNANDEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6027</v>
+        <v>0.6012999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6027</v>
+        <v>-1.9188</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>2.5201</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6027</v>
+        <v>-0.5044999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>0.7008</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6027</v>
+        <v>-1.2053</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6027</v>
+        <v>-1.3444</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>-0.6653</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6027</v>
+        <v>-0.6791</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>0.8399</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1.3661</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>-0.5262</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>0.7929</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.784</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>0.3129</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>0.4168</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>-0.1039</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. STACHOVSKIJ</t>
+          <t>R. REVELLES DIAZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2237</v>
+        <v>-0.2196</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.5039</v>
+        <v>-0.7653</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2803</v>
+        <v>0.5457</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3185</v>
+        <v>-1.2172</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3568</v>
+        <v>-0.5743</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.0384</v>
+        <v>-0.6428</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1367</v>
+        <v>-0.6443</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.149</v>
+        <v>-0.652</v>
       </c>
       <c r="L21" t="n">
-        <v>1.2857</v>
+        <v>0.0078</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1818</v>
+        <v>-0.5729</v>
       </c>
       <c r="N21" t="n">
-        <v>1.5059</v>
+        <v>0.07770000000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.3241</v>
+        <v>-0.6506</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.7929</v>
+        <v>0.7929</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.9733</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.1805</v>
+        <v>0.7929</v>
       </c>
       <c r="S21" t="n">
-        <v>0.8542999999999999</v>
+        <v>0.2047</v>
       </c>
       <c r="T21" t="n">
-        <v>1.3327</v>
+        <v>-0.121</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4785</v>
+        <v>0.3257</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. REVELLES DIAZ</t>
+          <t>D. STACHOVSKIJ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.9921</v>
+        <v>-0.3327</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.1727</v>
+        <v>-1.8095</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1807</v>
+        <v>1.4768</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.2172</v>
+        <v>0.3185</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.5743</v>
+        <v>0.3568</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6428</v>
+        <v>-0.0384</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6443</v>
+        <v>0.1367</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.652</v>
+        <v>-1.149</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0078</v>
+        <v>1.2857</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.5729</v>
+        <v>0.1818</v>
       </c>
       <c r="N22" t="n">
-        <v>0.07770000000000001</v>
+        <v>1.5059</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6506</v>
+        <v>-1.3241</v>
       </c>
       <c r="P22" t="n">
-        <v>0.7929</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-2.9733</v>
       </c>
       <c r="R22" t="n">
-        <v>0.7929</v>
+        <v>2.1805</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5678</v>
+        <v>0.7452</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5285</v>
+        <v>1.0271</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0393</v>
+        <v>-0.2819</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.2776</v>
+        <v>-1.3618</v>
       </c>
       <c r="E23" t="n">
         <v>-1.5172</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2396</v>
+        <v>0.1553</v>
       </c>
       <c r="G23" t="n">
         <v>-1.2376</v>
@@ -2248,13 +2248,13 @@
         <v>0.3964</v>
       </c>
       <c r="S23" t="n">
-        <v>0.8212</v>
+        <v>0.737</v>
       </c>
       <c r="T23" t="n">
         <v>0.2534</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5678</v>
+        <v>0.4836</v>
       </c>
       <c r="V23" t="n">
         <v>-0.2666</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>L. SIGISMONTI RODRIGUEZ</t>
+          <t>P. AVALOS ORTIZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,58 +2281,58 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.9919</v>
+        <v>-1.4531</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.2554</v>
+        <v>-3.6612</v>
       </c>
       <c r="F24" t="n">
-        <v>3.2635</v>
+        <v>2.2081</v>
       </c>
       <c r="G24" t="n">
-        <v>0.012</v>
+        <v>-2.3943</v>
       </c>
       <c r="H24" t="n">
-        <v>2.0419</v>
+        <v>-0.5099</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.0299</v>
+        <v>-1.8845</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.311</v>
+        <v>-3.2342</v>
       </c>
       <c r="K24" t="n">
-        <v>0.6059</v>
+        <v>-1.876</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.9169</v>
+        <v>-1.3583</v>
       </c>
       <c r="M24" t="n">
-        <v>1.323</v>
+        <v>0.8399</v>
       </c>
       <c r="N24" t="n">
-        <v>1.436</v>
+        <v>1.3661</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.113</v>
+        <v>-0.5262</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.7929</v>
+        <v>1.784</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.9733</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.1805</v>
+        <v>1.784</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5371</v>
+        <v>-0.1688</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2972</v>
+        <v>0.247</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2399</v>
+        <v>-0.4158</v>
       </c>
       <c r="V24" t="n">
         <v>-0.674</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>P. AVALOS ORTIZ</t>
+          <t>L. SIGISMONTI RODRIGUEZ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,58 +2359,58 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.1237</v>
+        <v>-1.7706</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.9668</v>
+        <v>-4.9498</v>
       </c>
       <c r="F25" t="n">
-        <v>1.8431</v>
+        <v>3.1793</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.3943</v>
+        <v>0.012</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.5099</v>
+        <v>2.0419</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.8845</v>
+        <v>-2.0299</v>
       </c>
       <c r="J25" t="n">
-        <v>-3.2342</v>
+        <v>-1.311</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.876</v>
+        <v>0.6059</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.3583</v>
+        <v>-1.9169</v>
       </c>
       <c r="M25" t="n">
-        <v>0.8399</v>
+        <v>1.323</v>
       </c>
       <c r="N25" t="n">
-        <v>1.3661</v>
+        <v>1.436</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.5262</v>
+        <v>-0.113</v>
       </c>
       <c r="P25" t="n">
-        <v>1.784</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>-2.9733</v>
       </c>
       <c r="R25" t="n">
-        <v>1.784</v>
+        <v>2.1805</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.8395</v>
+        <v>-0.3157</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.0586</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.7809</v>
+        <v>-0.3241</v>
       </c>
       <c r="V25" t="n">
         <v>-0.674</v>
@@ -2437,16 +2437,16 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>8.3391</v>
+        <v>8.385699999999998</v>
       </c>
       <c r="E26" t="n">
-        <v>-11.5951</v>
+        <v>-11.5953</v>
       </c>
       <c r="F26" t="n">
-        <v>19.9342</v>
+        <v>19.981</v>
       </c>
       <c r="G26" t="n">
-        <v>2.035599999999999</v>
+        <v>2.0356</v>
       </c>
       <c r="H26" t="n">
         <v>4.016</v>
@@ -2455,22 +2455,22 @@
         <v>-1.9803</v>
       </c>
       <c r="J26" t="n">
-        <v>-2.3939</v>
+        <v>-2.393900000000001</v>
       </c>
       <c r="K26" t="n">
         <v>-4.2317</v>
       </c>
       <c r="L26" t="n">
-        <v>1.838</v>
+        <v>1.838000000000001</v>
       </c>
       <c r="M26" t="n">
         <v>4.429399999999999</v>
       </c>
       <c r="N26" t="n">
-        <v>8.2477</v>
+        <v>8.247700000000002</v>
       </c>
       <c r="O26" t="n">
-        <v>-3.8181</v>
+        <v>-3.818100000000001</v>
       </c>
       <c r="P26" t="n">
         <v>1.9822</v>
@@ -2482,13 +2482,13 @@
         <v>17.8401</v>
       </c>
       <c r="S26" t="n">
-        <v>3.3957</v>
+        <v>3.4424</v>
       </c>
       <c r="T26" t="n">
-        <v>1.9837</v>
+        <v>1.9839</v>
       </c>
       <c r="U26" t="n">
-        <v>1.4115</v>
+        <v>1.4586</v>
       </c>
       <c r="V26" t="n">
         <v>0.9253000000000003</v>
